--- a/templates/odoo-template.xlsx
+++ b/templates/odoo-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\momeni-01\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Momeni\project\timesheets-web\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B718597E-757D-414D-9D39-1278A29FDFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55698ED-AFD1-4314-9668-AD5942F8CFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2F10141-EE7C-4AE3-81AF-CB918D8F0B04}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>BI (business intelligence)</t>
   </si>
@@ -51,6 +49,21 @@
   </si>
   <si>
     <t>تست222</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>quantity</t>
   </si>
 </sst>
 </file>
@@ -426,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D182FC-F845-4D87-B54D-2419D26ABEB5}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -434,36 +447,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>46186</v>
+      <c r="A1" t="s">
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>2.5</v>
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46187</v>
+        <v>46186</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
